--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onkologie-to-mvgenomseq.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onkologie-to-mvgenomseq.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -118,7 +118,7 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-diagnose-primaertumor|2025.0.4</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-diagnose-primaertumor|2026.0.3</t>
   </si>
   <si>
     <t/>
@@ -136,7 +136,7 @@
     <t>equivalent</t>
   </si>
   <si>
-    <t>diagnosisOd.mainDiagnosis</t>
+    <t>diagnosisOD.mainDiagnosis</t>
   </si>
   <si>
     <t>Haupttumordiagnose</t>
@@ -148,7 +148,7 @@
     <t>Feststellungsdatum</t>
   </si>
   <si>
-    <t>diagnosisOd.mainDiagnosis.date</t>
+    <t>diagnosisOD.diagnosisDate</t>
   </si>
   <si>
     <t>Datum der Diagnose</t>
@@ -160,7 +160,7 @@
     <t>ICD-O-3 Topographie</t>
   </si>
   <si>
-    <t>diagnosisOd.mainDiagnosis.icdoTopography</t>
+    <t>diagnosisOD.topography.code</t>
   </si>
   <si>
     <t>Condition.bodySite.coding:icd-o-3.version</t>
@@ -169,7 +169,7 @@
     <t>ICD-O-3 Version</t>
   </si>
   <si>
-    <t>diagnosisOd.mainDiagnosis.icdoVersion</t>
+    <t>diagnosisOD.topography.version</t>
   </si>
   <si>
     <t>Condition.extension:morphology-behavior-icdo3.valueCodeableConcept.coding.code</t>
@@ -178,13 +178,13 @@
     <t>ICD-O-3 Morphologie-Code</t>
   </si>
   <si>
-    <t>DiagnosisOd.mainDiagnosis.icdoMorphology</t>
+    <t>diagnosisOD.histology.code</t>
   </si>
   <si>
     <t>ICD-O-3 Morphologie</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-diagnose/StructureDefinition/Diagnose|2025.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-diagnose/StructureDefinition/Diagnose|2026.0.3</t>
   </si>
   <si>
     <t>Condition.code.coding</t>
@@ -196,19 +196,13 @@
     <t>source-is-broader-than-target</t>
   </si>
   <si>
-    <t>DiagnosisOd.additionalDiagnoses</t>
-  </si>
-  <si>
-    <t>DiagnosisOd.additionalDiagnoses.date</t>
-  </si>
-  <si>
-    <t>Condition.code.coding"</t>
-  </si>
-  <si>
-    <t>DiagnosisOd.germlineDiagnoses</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-allgemeiner-leistungszustand-ecog|2025.0.4</t>
+    <t>diagnosisOD.additionalDiagnoses</t>
+  </si>
+  <si>
+    <t>diagnosisOD.germlineDiagnosisCode</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-allgemeiner-leistungszustand-ecog|2026.0.3</t>
   </si>
   <si>
     <t>Observation.valueCodeableConcept.coding.code</t>
@@ -217,19 +211,19 @@
     <t>ECOG-Performance-Status</t>
   </si>
   <si>
-    <t>ecogPerformanceStatusScore</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-grading|2025.0.4</t>
+    <t>diagnosisOD.ECOGPerformanceStatusScore</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-grading|2026.0.3</t>
   </si>
   <si>
     <t>Histologisches Grading</t>
   </si>
   <si>
-    <t>grading</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tnm-klassifikation|2025.0.4</t>
+    <t>diagnosisOD.grading</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tnm-klassifikation|2026.0.3</t>
   </si>
   <si>
     <t>TNM-Klassifikation</t>
@@ -647,7 +641,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -703,35 +697,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>60</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E5" t="s" s="2">
         <v>57</v>
       </c>
     </row>
@@ -764,7 +741,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -781,19 +758,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="E3" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +802,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -842,19 +819,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +863,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -903,70 +880,70 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="E3" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="E4" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="E5" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="E6" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onkologie-to-mvgenomseq.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onkologie-to-mvgenomseq.xlsx
@@ -88,7 +88,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping der einzelnen MII-OnkologieProfile auf den Klinischen Datenkranz der MVGenomSeq</t>
+    <t>Mapping der einzelnen MII-Onkologieprofile auf den Klinischen Datenkranz der Modellvorhaben-Genomsequenzierung. ABGRENZUNG: Diese ConceptMap deckt bewusst nur OncologyCase.json ab — die klinischen Falldaten, die im KDS-Modul Onkologie gefuehrt werden. Die uebrigen Schemata des Datenkranzes (OncologyMolecular, OncologyPlan, OncologyFollowUp, Oncology) betreffen die molekulare Diagnostik und die Therapieplanung des Molekularen Tumorboards und werden im KDS-Modul MTB abgebildet, nicht hier. Zielfelder gegen mvgenomseq_schemas/2024-12/OncologyCase.json verifiziert.</t>
   </si>
   <si>
     <t>Purpose</t>
